--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755621354_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.03542774876735174</v>
       </c>
       <c r="C2" t="n">
-        <v>149106528</v>
+        <v>6212772</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>149106528</v>
+        <v>6212772</v>
       </c>
       <c r="K2" t="n">
-        <v>98192038</v>
+        <v>3530901</v>
       </c>
       <c r="L2" t="n">
-        <v>53905390</v>
+        <v>1674587</v>
       </c>
       <c r="M2" t="n">
-        <v>13049744</v>
+        <v>336855</v>
       </c>
       <c r="N2" t="n">
-        <v>666292</v>
+        <v>11781</v>
       </c>
       <c r="O2" t="n">
-        <v>7983626</v>
+        <v>216429</v>
       </c>
       <c r="P2" t="n">
-        <v>3317590</v>
+        <v>95181</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9998975992202759</v>
+        <v>0.9997932314872742</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8341099619865417</v>
+        <v>0.719780445098877</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6876384615898132</v>
+        <v>0.5125172138214111</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5939447283744812</v>
+        <v>0.3685785531997681</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4088493585586548</v>
+        <v>0.1745204031467438</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6527528762817383</v>
+        <v>0.4248787760734558</v>
       </c>
       <c r="W2" t="n">
-        <v>0.717576801776886</v>
+        <v>0.4941489696502686</v>
       </c>
       <c r="X2" t="n">
-        <v>149106528</v>
+        <v>6212772</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>149106528</v>
+        <v>6212772</v>
       </c>
       <c r="AF2" t="n">
-        <v>95964046</v>
+        <v>3493153</v>
       </c>
       <c r="AG2" t="n">
-        <v>50147674</v>
+        <v>1600240</v>
       </c>
       <c r="AH2" t="n">
-        <v>11935278</v>
+        <v>317977</v>
       </c>
       <c r="AI2" t="n">
-        <v>620924</v>
+        <v>11503</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7369486</v>
+        <v>204180</v>
       </c>
       <c r="AK2" t="n">
-        <v>3122182</v>
+        <v>89730</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.8097841143608093</v>
+        <v>0.7074398994445801</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.6521316170692444</v>
+        <v>0.4994371235370636</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5369819402694702</v>
+        <v>0.3433476388454437</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.2927406430244446</v>
+        <v>0.1301568299531937</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.6043883562088013</v>
+        <v>0.4018864035606384</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6731289029121399</v>
+        <v>0.4642896056175232</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.01012749337611102</v>
       </c>
       <c r="C3" t="n">
-        <v>4918</v>
+        <v>491</v>
       </c>
       <c r="D3" t="n">
-        <v>98192038</v>
+        <v>3530901</v>
       </c>
       <c r="E3" t="n">
-        <v>17467936</v>
+        <v>1144479</v>
       </c>
       <c r="F3" t="n">
-        <v>1049282</v>
+        <v>100043</v>
       </c>
       <c r="G3" t="n">
-        <v>121172</v>
+        <v>8902</v>
       </c>
       <c r="H3" t="n">
-        <v>108756</v>
+        <v>15182</v>
       </c>
       <c r="I3" t="n">
-        <v>17858</v>
+        <v>2903</v>
       </c>
       <c r="J3" t="n">
-        <v>236567798</v>
+        <v>9856343</v>
       </c>
       <c r="K3" t="n">
-        <v>249198944</v>
+        <v>9892875</v>
       </c>
       <c r="L3" t="n">
-        <v>283030390</v>
+        <v>11161433</v>
       </c>
       <c r="M3" t="n">
-        <v>354345116</v>
+        <v>14550769</v>
       </c>
       <c r="N3" t="n">
-        <v>382590742</v>
+        <v>15925105</v>
       </c>
       <c r="O3" t="n">
-        <v>369197542</v>
+        <v>15265066</v>
       </c>
       <c r="P3" t="n">
-        <v>379738676</v>
+        <v>15778915</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8395211696624756</v>
+        <v>0.7351600527763367</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6895692944526672</v>
+        <v>0.5049751400947571</v>
       </c>
       <c r="T3" t="n">
-        <v>0.581982433795929</v>
+        <v>0.357384592294693</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3120113015174866</v>
+        <v>0.1315269470214844</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6519916653633118</v>
+        <v>0.4224051535129547</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7141990065574646</v>
+        <v>0.4904972910881042</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>95964046</v>
+        <v>3493153</v>
       </c>
       <c r="Z3" t="n">
-        <v>19045758</v>
+        <v>1148330</v>
       </c>
       <c r="AA3" t="n">
-        <v>1400700</v>
+        <v>117926</v>
       </c>
       <c r="AB3" t="n">
-        <v>382236</v>
+        <v>21139</v>
       </c>
       <c r="AC3" t="n">
-        <v>143170</v>
+        <v>18489</v>
       </c>
       <c r="AD3" t="n">
-        <v>26050</v>
+        <v>3864</v>
       </c>
       <c r="AE3" t="n">
-        <v>236583072</v>
+        <v>9857628</v>
       </c>
       <c r="AF3" t="n">
-        <v>246185974</v>
+        <v>9822914</v>
       </c>
       <c r="AG3" t="n">
-        <v>280766638</v>
+        <v>11150376</v>
       </c>
       <c r="AH3" t="n">
-        <v>352975368</v>
+        <v>14519713</v>
       </c>
       <c r="AI3" t="n">
-        <v>382053978</v>
+        <v>15903954</v>
       </c>
       <c r="AJ3" t="n">
-        <v>368620808</v>
+        <v>15254153</v>
       </c>
       <c r="AK3" t="n">
-        <v>379528280</v>
+        <v>15772817</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.8204723000526428</v>
+        <v>0.7273006439208984</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.6414998173713684</v>
+        <v>0.4825556576251984</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5322803258895874</v>
+        <v>0.3373560905456543</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.2907663583755493</v>
+        <v>0.1284232586622238</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.6018372178077698</v>
+        <v>0.3984987437725067</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6721322536468506</v>
+        <v>0.4624066054821014</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.07793949739483971</v>
       </c>
       <c r="C4" t="n">
-        <v>1898</v>
+        <v>195</v>
       </c>
       <c r="D4" t="n">
-        <v>17990058</v>
+        <v>1223084</v>
       </c>
       <c r="E4" t="n">
-        <v>53905390</v>
+        <v>1674587</v>
       </c>
       <c r="F4" t="n">
-        <v>5078056</v>
+        <v>309252</v>
       </c>
       <c r="G4" t="n">
-        <v>217436</v>
+        <v>15903</v>
       </c>
       <c r="H4" t="n">
-        <v>848406</v>
+        <v>78488</v>
       </c>
       <c r="I4" t="n">
-        <v>131304</v>
+        <v>14668</v>
       </c>
       <c r="J4" t="n">
-        <v>15274</v>
+        <v>1285</v>
       </c>
       <c r="K4" t="n">
-        <v>19528696</v>
+        <v>1374624</v>
       </c>
       <c r="L4" t="n">
-        <v>24486662</v>
+        <v>1592790</v>
       </c>
       <c r="M4" t="n">
-        <v>8921566</v>
+        <v>577075</v>
       </c>
       <c r="N4" t="n">
-        <v>963384</v>
+        <v>55724</v>
       </c>
       <c r="O4" t="n">
-        <v>4247076</v>
+        <v>292961</v>
       </c>
       <c r="P4" t="n">
-        <v>1305734</v>
+        <v>97435</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999487996101379</v>
+        <v>0.9998965859413147</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8368067741394043</v>
+        <v>0.7273889183998108</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6886025667190552</v>
+        <v>0.5087182521820068</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5879027247428894</v>
+        <v>0.362895280122757</v>
       </c>
       <c r="U4" t="n">
-        <v>0.353925883769989</v>
+        <v>0.1500038206577301</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6523720622062683</v>
+        <v>0.4236383438110352</v>
       </c>
       <c r="W4" t="n">
-        <v>0.7158839702606201</v>
+        <v>0.492316335439682</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>20632298</v>
+        <v>1270840</v>
       </c>
       <c r="Z4" t="n">
-        <v>50147674</v>
+        <v>1600240</v>
       </c>
       <c r="AA4" t="n">
-        <v>5814690</v>
+        <v>320069</v>
       </c>
       <c r="AB4" t="n">
-        <v>397612</v>
+        <v>23306</v>
       </c>
       <c r="AC4" t="n">
-        <v>1014446</v>
+        <v>85088</v>
       </c>
       <c r="AD4" t="n">
-        <v>165828</v>
+        <v>16634</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>22541666</v>
+        <v>1444585</v>
       </c>
       <c r="AG4" t="n">
-        <v>26750414</v>
+        <v>1603847</v>
       </c>
       <c r="AH4" t="n">
-        <v>10291314</v>
+        <v>608131</v>
       </c>
       <c r="AI4" t="n">
-        <v>1500148</v>
+        <v>76875</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4823810</v>
+        <v>303874</v>
       </c>
       <c r="AK4" t="n">
-        <v>1516130</v>
+        <v>103533</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.8150931596755981</v>
+        <v>0.7172327637672424</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.646772027015686</v>
+        <v>0.4908512830734253</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5346208214759827</v>
+        <v>0.3403254747390747</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.2917501628398895</v>
+        <v>0.1292842328548431</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.6031100153923035</v>
+        <v>0.4001854360103607</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.672630250453949</v>
+        <v>0.4633462131023407</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>2900</v>
+        <v>241</v>
       </c>
       <c r="D5" t="n">
-        <v>1100700</v>
+        <v>111738</v>
       </c>
       <c r="E5" t="n">
-        <v>5560418</v>
+        <v>322934</v>
       </c>
       <c r="F5" t="n">
-        <v>13049744</v>
+        <v>336855</v>
       </c>
       <c r="G5" t="n">
-        <v>341802</v>
+        <v>16922</v>
       </c>
       <c r="H5" t="n">
-        <v>2059752</v>
+        <v>126677</v>
       </c>
       <c r="I5" t="n">
-        <v>307602</v>
+        <v>27189</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>18769922</v>
+        <v>1272000</v>
       </c>
       <c r="L5" t="n">
-        <v>24267158</v>
+        <v>1641590</v>
       </c>
       <c r="M5" t="n">
-        <v>9373174</v>
+        <v>605701</v>
       </c>
       <c r="N5" t="n">
-        <v>1469182</v>
+        <v>77790</v>
       </c>
       <c r="O5" t="n">
-        <v>4261356</v>
+        <v>295944</v>
       </c>
       <c r="P5" t="n">
-        <v>1327600</v>
+        <v>98869</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999604225158691</v>
+        <v>0.9999200105667114</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9007009267807007</v>
+        <v>0.8353106379508972</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8735930919647217</v>
+        <v>0.7987368106842041</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9525661468505859</v>
+        <v>0.926400363445282</v>
       </c>
       <c r="U5" t="n">
-        <v>0.993692934513092</v>
+        <v>0.9916919469833374</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9779396653175354</v>
+        <v>0.9633546471595764</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9931724071502686</v>
+        <v>0.987784743309021</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1370572</v>
+        <v>127400</v>
       </c>
       <c r="Z5" t="n">
-        <v>6035332</v>
+        <v>321330</v>
       </c>
       <c r="AA5" t="n">
-        <v>11935278</v>
+        <v>317977</v>
       </c>
       <c r="AB5" t="n">
-        <v>403974</v>
+        <v>18196</v>
       </c>
       <c r="AC5" t="n">
-        <v>2311314</v>
+        <v>128388</v>
       </c>
       <c r="AD5" t="n">
-        <v>366448</v>
+        <v>29265</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>20997914</v>
+        <v>1309748</v>
       </c>
       <c r="AG5" t="n">
-        <v>28024874</v>
+        <v>1715937</v>
       </c>
       <c r="AH5" t="n">
-        <v>10487640</v>
+        <v>624579</v>
       </c>
       <c r="AI5" t="n">
-        <v>1514550</v>
+        <v>78068</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4875496</v>
+        <v>308193</v>
       </c>
       <c r="AK5" t="n">
-        <v>1523008</v>
+        <v>104320</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.8871123790740967</v>
+        <v>0.8286083340644836</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.8579809069633484</v>
+        <v>0.7934224605560303</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9461252093315125</v>
+        <v>0.9232931137084961</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9921836256980896</v>
+        <v>0.9903584718704224</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9748520255088806</v>
+        <v>0.9619134068489075</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9921202659606934</v>
+        <v>0.9870660901069641</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>3762</v>
+        <v>237</v>
       </c>
       <c r="D6" t="n">
-        <v>304784</v>
+        <v>19189</v>
       </c>
       <c r="E6" t="n">
-        <v>420798</v>
+        <v>24714</v>
       </c>
       <c r="F6" t="n">
-        <v>432870</v>
+        <v>17376</v>
       </c>
       <c r="G6" t="n">
-        <v>666292</v>
+        <v>11781</v>
       </c>
       <c r="H6" t="n">
-        <v>258770</v>
+        <v>12986</v>
       </c>
       <c r="I6" t="n">
-        <v>48198</v>
+        <v>3288</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>351084</v>
+        <v>20393</v>
       </c>
       <c r="Z6" t="n">
-        <v>419236</v>
+        <v>24197</v>
       </c>
       <c r="AA6" t="n">
-        <v>411478</v>
+        <v>17122</v>
       </c>
       <c r="AB6" t="n">
-        <v>620924</v>
+        <v>11503</v>
       </c>
       <c r="AC6" t="n">
-        <v>278344</v>
+        <v>12946</v>
       </c>
       <c r="AD6" t="n">
-        <v>54408</v>
+        <v>3410</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>1182</v>
+        <v>87</v>
       </c>
       <c r="D7" t="n">
-        <v>123996</v>
+        <v>18620</v>
       </c>
       <c r="E7" t="n">
-        <v>935940</v>
+        <v>88664</v>
       </c>
       <c r="F7" t="n">
-        <v>2155056</v>
+        <v>128381</v>
       </c>
       <c r="G7" t="n">
-        <v>244410</v>
+        <v>10805</v>
       </c>
       <c r="H7" t="n">
-        <v>7983626</v>
+        <v>216429</v>
       </c>
       <c r="I7" t="n">
-        <v>800772</v>
+        <v>49387</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>172422</v>
+        <v>22972</v>
       </c>
       <c r="Z7" t="n">
-        <v>1122264</v>
+        <v>96320</v>
       </c>
       <c r="AA7" t="n">
-        <v>2407778</v>
+        <v>127732</v>
       </c>
       <c r="AB7" t="n">
-        <v>269636</v>
+        <v>10809</v>
       </c>
       <c r="AC7" t="n">
-        <v>7369486</v>
+        <v>204180</v>
       </c>
       <c r="AD7" t="n">
-        <v>903396</v>
+        <v>50360</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>614</v>
+        <v>34</v>
       </c>
       <c r="D8" t="n">
-        <v>9158</v>
+        <v>1993</v>
       </c>
       <c r="E8" t="n">
-        <v>101570</v>
+        <v>11999</v>
       </c>
       <c r="F8" t="n">
-        <v>206302</v>
+        <v>22023</v>
       </c>
       <c r="G8" t="n">
-        <v>38564</v>
+        <v>3192</v>
       </c>
       <c r="H8" t="n">
-        <v>971392</v>
+        <v>59628</v>
       </c>
       <c r="I8" t="n">
-        <v>3317590</v>
+        <v>95181</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>15290</v>
+        <v>2980</v>
       </c>
       <c r="Z8" t="n">
-        <v>127824</v>
+        <v>13670</v>
       </c>
       <c r="AA8" t="n">
-        <v>256668</v>
+        <v>25282</v>
       </c>
       <c r="AB8" t="n">
-        <v>46690</v>
+        <v>3425</v>
       </c>
       <c r="AC8" t="n">
-        <v>1076536</v>
+        <v>58963</v>
       </c>
       <c r="AD8" t="n">
-        <v>3122182</v>
+        <v>89730</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
